--- a/Экономика/ЛР1.xlsx
+++ b/Экономика/ЛР1.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\labs\labs-6-sem\Экономика\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Udalit\Лабы\Экономіка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB52A11-ABBF-49CA-9963-DB49EC4A62DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>Задача 2 вариант</t>
   </si>
@@ -266,15 +266,81 @@
   </si>
   <si>
     <t>ПП=</t>
+  </si>
+  <si>
+    <t>Потрачено</t>
+  </si>
+  <si>
+    <t>Прібыль</t>
+  </si>
+  <si>
+    <t>План</t>
+  </si>
+  <si>
+    <t>отчёт</t>
+  </si>
+  <si>
+    <t>Рассчитать показатели использования Оборотных средств (ОбС)</t>
+  </si>
+  <si>
+    <t>Задача 1</t>
+  </si>
+  <si>
+    <t>Длительность оборота оборотных средств факт, дни</t>
+  </si>
+  <si>
+    <t>Длительность оборота оборотных средств план, дни</t>
+  </si>
+  <si>
+    <t>Средний остаток ОбС за период, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Число дней в периодне, дни</t>
+  </si>
+  <si>
+    <t>Реализованная продукция факт, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Реализованная продукция план, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Прирост реализованной продукции, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Задача 2</t>
+  </si>
+  <si>
+    <t>Реализованная продукция, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Средний остаток ОбС за период факт, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Коэффициент оборачиваемости факт</t>
+  </si>
+  <si>
+    <t>Коэффициент оборачиваемости план</t>
+  </si>
+  <si>
+    <t>Длительность одного оборота ОбС факт, дни</t>
+  </si>
+  <si>
+    <t>Длительность одного оборота ОбСплан, дни</t>
+  </si>
+  <si>
+    <t>Средний остаток ОбС за период план, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Размер высвобождаемых ОбС, тыс. руб.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -549,14 +615,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
@@ -580,17 +640,11 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
@@ -621,26 +675,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -650,9 +698,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -664,10 +709,62 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1" xr:uid="{B26B792A-DE64-4259-92D0-5213C489A081}"/>
+    <cellStyle name="Обычный 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -944,523 +1041,519 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" customWidth="1"/>
-    <col min="15" max="15" width="16.21875" customWidth="1"/>
-    <col min="16" max="16" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="18.75" customWidth="1"/>
+    <col min="6" max="6" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="9.5" customWidth="1"/>
+    <col min="15" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="16" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="49" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>950</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <f>12-MONTH(D5)+1</f>
         <v>12</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>42</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="6">
         <v>44958</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <f>MONTH(G5)</f>
         <v>2</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="7">
         <f>B5/$B$12*100</f>
         <v>17.887403502165316</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <f>B5+C5-F5</f>
         <v>908</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="7">
         <f>J5/$J$12*100</f>
         <v>16.554238833181405</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <f>B5+(C5*E5/12)-(F5*(12-H5)/12)</f>
         <v>915</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>236</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>13</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>44986</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <f>12-MONTH(D6)</f>
         <v>9</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>30</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>45139</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <f t="shared" ref="H6:H11" si="0">MONTH(G6)</f>
         <v>8</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <f t="shared" ref="I6:I11" si="1">B6/$B$12*100</f>
         <v>4.4436076068536998</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <f t="shared" ref="J6:J11" si="2">B6+C6-F6</f>
         <v>219</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="7">
         <f t="shared" ref="K6:K11" si="3">J6/$J$12*100</f>
         <v>3.9927073837739289</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <f t="shared" ref="L6:L11" si="4">B6+(C6*E6/12)-(F6*(12-H6)/12)</f>
         <v>235.75</v>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>2700</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>232</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>45047</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <f>12-MONTH(D7)+1</f>
         <v>8</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>15</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>45078</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
         <f t="shared" si="1"/>
         <v>50.837883637733007</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <f t="shared" si="2"/>
         <v>2917</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="7">
         <f t="shared" si="3"/>
         <v>53.181403828623516</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <f t="shared" si="4"/>
         <v>2847.1666666666665</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>630</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>17</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>45170</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <f>12-MONTH(D8)+1</f>
         <v>4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>8</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>45261</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <f t="shared" si="1"/>
         <v>11.862172848804368</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <f t="shared" si="2"/>
         <v>639</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="7">
         <f t="shared" si="3"/>
         <v>11.649954421148587</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <f t="shared" si="4"/>
         <v>635.66666666666663</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>225</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>0</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>0</v>
       </c>
-      <c r="E9" s="6">
-        <f t="shared" ref="E6:E11" si="5">12-MONTH(D9)+1</f>
+      <c r="E9" s="4">
+        <f t="shared" ref="E9:E11" si="5">12-MONTH(D9)+1</f>
         <v>12</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>16</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>44986</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <f t="shared" si="1"/>
         <v>4.236490303144417</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <f t="shared" si="2"/>
         <v>209</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="7">
         <f t="shared" si="3"/>
         <v>3.8103919781221509</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <f t="shared" si="4"/>
         <v>213</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>470</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>28</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>45078</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>10</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>45108</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <f t="shared" si="1"/>
         <v>8.8495575221238933</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <f t="shared" si="2"/>
         <v>488</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <f t="shared" si="3"/>
         <v>8.8969917958067448</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <f t="shared" si="4"/>
         <v>482.16666666666663</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>100</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>45017</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>45200</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <f t="shared" si="1"/>
         <v>1.8828845791752966</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="7">
         <f t="shared" si="3"/>
         <v>1.9143117593436645</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <f t="shared" si="4"/>
         <v>106.66666666666667</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="13">
         <f>SUM(B5:B11)</f>
         <v>5311</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <f>SUM(C5:C11)</f>
         <v>300</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="15">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="13">
         <f>SUM(F5:F11)</f>
         <v>126</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="13">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="11">
         <f>SUM(I5:I11)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="10">
         <f>SUM(J5:J11)</f>
         <v>5485</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="11">
         <f>SUM(K5:K11)</f>
         <v>100</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="10">
         <f>SUM(L5:L11)</f>
         <v>5435.416666666667</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="12">
         <f>C12/L12</f>
         <v>5.5193560751245686E-2</v>
       </c>
-      <c r="N12" s="14">
+      <c r="N12" s="12">
         <f>F12/L12</f>
         <v>2.3181295515523188E-2</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="11">
         <f>(L5+L6+L11)/L12*100</f>
         <v>23.133767727098505</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="11">
         <f>(L7+L8+L10+L9)/L12*100</f>
         <v>76.866232272901485</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="M3:M4"/>
@@ -1474,381 +1567,385 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367A3D55-18DA-42CD-903B-3CB675A5B1E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.625" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26">
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22">
         <v>2</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16">
         <v>1320</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16">
         <v>8</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16">
         <v>14</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16">
         <v>11</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16">
         <v>16</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16">
         <v>222000</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17">
         <v>44958</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38">
-        <f t="shared" ref="C13:K13" si="0">12-MONTH(C12)+1</f>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33">
+        <f t="shared" ref="C13" si="0">12-MONTH(C12)+1</f>
         <v>11</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16">
         <v>780000</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17">
         <v>45122</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30">
+      <c r="B16" s="26"/>
+      <c r="C16" s="26">
         <f>6.5</f>
         <v>6.5</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-    </row>
-    <row r="17" spans="1:11" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16">
         <v>155</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29">
         <f>((C6-C7-C8-C9-C10)*1000+C11*C13/12-C14*(12-C16)/12)/1000</f>
         <v>1117</v>
       </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29">
         <f>(C17)/(C18)*100</f>
         <v>13.876454789615039</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30">
         <v>6</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29">
         <f>C17*C20</f>
         <v>930</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36">
+      <c r="B22" s="32"/>
+      <c r="C22" s="32">
         <f>C21/C18</f>
         <v>0.83258728737690246</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1860,494 +1957,554 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960101A1-2F05-4BBA-8571-1D295763EEB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="15" max="15" width="28.44140625" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="40" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="1:17" ht="35.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="40"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46">
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+    </row>
+    <row r="5" spans="1:17" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40">
         <v>2</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="O5" s="52" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="O5" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="55">
+      <c r="P5" s="48">
         <v>2</v>
       </c>
-      <c r="Q5" s="50"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
+      <c r="Q5" s="43"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="O6" s="53" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="O6" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="51"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+      <c r="P6" s="42">
+        <f>P18/P12*100</f>
+        <v>93.554511219694376</v>
+      </c>
+      <c r="Q6" s="44"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="O7" s="53" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="O7" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="51"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
+      <c r="P7" s="42">
+        <f>P19/P13*100</f>
+        <v>106.88955422488355</v>
+      </c>
+      <c r="Q7" s="44"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41">
         <v>2500</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="O8" s="53" t="s">
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="O8" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="51"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="P8" s="42">
+        <f t="shared" ref="P7:P10" si="0">P20/P14*100</f>
+        <v>118.27956989247311</v>
+      </c>
+      <c r="Q8" s="44"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41">
         <v>1100</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="O9" s="53" t="s">
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="O9" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="51"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
+      <c r="P9" s="42">
+        <f>P21/P15*100</f>
+        <v>119.20063349170624</v>
+      </c>
+      <c r="Q9" s="44"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41">
         <v>5000</v>
       </c>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="O10" s="53" t="s">
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="O10" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="51"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="P10" s="42">
+        <f>P22/P16*100</f>
+        <v>119.76911976911975</v>
+      </c>
+      <c r="Q10" s="44"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="O11" s="54" t="s">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="O11" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="51"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+      <c r="P11" s="42"/>
+      <c r="Q11" s="44"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41">
         <v>200</v>
       </c>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="O12" s="53" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="O12" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="51"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
+      <c r="P12" s="42">
+        <f>M20/(C19*1000)</f>
+        <v>2.0570422535211268</v>
+      </c>
+      <c r="Q12" s="44"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41">
         <v>110</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="O13" s="53" t="s">
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="O13" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="51"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="P13" s="42">
+        <f>C19*1000/M20</f>
+        <v>0.48613488531324889</v>
+      </c>
+      <c r="Q13" s="44"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41">
         <v>460</v>
       </c>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="O14" s="53" t="s">
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="O14" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="51"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+      <c r="P14" s="42">
+        <f>(C19*1000)/C21</f>
+        <v>217.79141104294479</v>
+      </c>
+      <c r="Q14" s="44"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="O15" s="53" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="O15" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="51"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
+      <c r="P15" s="42">
+        <f>((C19-C20)*1000)/C21</f>
+        <v>197.85276073619633</v>
+      </c>
+      <c r="Q15" s="44"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41">
         <v>110</v>
       </c>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="O16" s="53" t="s">
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="O16" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="51"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="47" t="s">
+      <c r="P16" s="42">
+        <f>(M22/(C19*1000))*100</f>
+        <v>44.366197183098592</v>
+      </c>
+      <c r="Q16" s="44"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41">
         <v>60</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-      <c r="O17" s="54" t="s">
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="O17" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="51"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="s">
+      <c r="P17" s="42"/>
+      <c r="Q17" s="44"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41">
         <v>390</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="O18" s="53" t="s">
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="O18" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="P18" s="49">
+      <c r="P18" s="42">
         <f>M24/(D35*1000)</f>
         <v>1.9244558258642765</v>
       </c>
-      <c r="Q18" s="51"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="Q18" s="44"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41">
         <v>1420</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="O19" s="53" t="s">
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" t="s">
+        <v>79</v>
+      </c>
+      <c r="O19" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="P19" s="49">
+      <c r="P19" s="42">
         <f>D35*1000/M24</f>
         <v>0.51962741184298067</v>
       </c>
-      <c r="Q19" s="51"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="47" t="s">
+      <c r="Q19" s="44"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41">
         <v>130</v>
       </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="O20" s="53" t="s">
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20">
+        <f>(C8*C12+C9*C13+C10*C14)</f>
+        <v>2921000</v>
+      </c>
+      <c r="O20" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="P20" s="49">
-        <f>D35*1000/C21</f>
-        <v>239.57055214723925</v>
-      </c>
-      <c r="Q20" s="51"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="47" t="s">
+      <c r="P20" s="42">
+        <f>D35*1000/E37</f>
+        <v>257.60274424434328</v>
+      </c>
+      <c r="Q20" s="44"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41">
         <v>6520</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="O21" s="53" t="s">
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21">
+        <f>C8*C16+C9*C17+C10*C18</f>
+        <v>2291000</v>
+      </c>
+      <c r="O21" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="P21" s="49">
-        <f>D35-D36/D37</f>
-        <v>1561.4866345311132</v>
-      </c>
-      <c r="Q21" s="51"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="46" t="s">
+      <c r="P21" s="42">
+        <f>((D35-D36)*1000)/E37</f>
+        <v>235.84174417837588</v>
+      </c>
+      <c r="Q21" s="44"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="O22" s="53" t="s">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22">
+        <f>M20-M21</f>
+        <v>630000</v>
+      </c>
+      <c r="O22" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="51"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="47" t="s">
+      <c r="P22" s="42">
+        <f>(M26/(D35*1000)*100)</f>
+        <v>53.137003841229188</v>
+      </c>
+      <c r="Q22" s="44"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="47" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41">
         <v>2600</v>
       </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
       <c r="L24" t="s">
         <v>75</v>
       </c>
@@ -2356,231 +2513,248 @@
         <v>3006000</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="47" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41">
         <v>1200</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="47" t="s">
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25">
+        <f>C24*C32+C25*C33+C26*C34</f>
+        <v>2176000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41">
         <v>5200</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M26">
+        <f>M24-M25</f>
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41">
         <v>210</v>
       </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="47" t="s">
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41">
         <v>100</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="47" t="s">
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47">
+      <c r="B30" s="41"/>
+      <c r="C30" s="41">
         <v>450</v>
       </c>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="47" t="s">
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="47" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47">
+      <c r="B32" s="41"/>
+      <c r="C32" s="41">
         <v>100</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="47" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41">
         <v>80</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="47" t="s">
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47">
+      <c r="B34" s="41"/>
+      <c r="C34" s="41">
         <v>350</v>
       </c>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="47" t="s">
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47">
+      <c r="B35" s="41"/>
+      <c r="C35" s="41">
         <v>10</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="41">
         <f>C19+(C19*C35/100)</f>
         <v>1562</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="47" t="s">
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47">
+      <c r="B36" s="41"/>
+      <c r="C36" s="41">
         <v>1.5</v>
       </c>
-      <c r="D36" s="47">
-        <f>D35*C36/C35</f>
-        <v>234.3</v>
-      </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="47" t="s">
+      <c r="D36" s="41">
+        <f>C20*(C36/100)+C20</f>
+        <v>131.94999999999999</v>
+      </c>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47">
+      <c r="B37" s="41"/>
+      <c r="C37" s="41">
         <v>7</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="41">
         <f>C21*C37/100</f>
         <v>456.4</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="47"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="47"/>
-      <c r="K37" s="47"/>
+      <c r="E37" s="41">
+        <f>C21-D37</f>
+        <v>6063.6</v>
+      </c>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2589,4 +2763,399 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="59"/>
+      <c r="B4" s="61">
+        <v>2</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+    </row>
+    <row r="5" spans="1:11" ht="77.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="63">
+        <v>66</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:11" ht="77.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="63">
+        <v>40</v>
+      </c>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="63">
+        <v>123</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="63">
+        <v>180</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="66">
+        <f>(B8/B5)*B7</f>
+        <v>335.45454545454544</v>
+      </c>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="66">
+        <f>(B8/B6)*B7</f>
+        <v>553.5</v>
+      </c>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="66">
+        <f>B10-B9</f>
+        <v>218.04545454545456</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="66"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="70"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="59"/>
+      <c r="B15" s="61">
+        <v>2</v>
+      </c>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="64" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="63">
+        <v>670</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="63">
+        <v>195</v>
+      </c>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="63">
+        <v>360</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="66">
+        <f>B16/B17</f>
+        <v>3.4358974358974357</v>
+      </c>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="69">
+        <v>5</v>
+      </c>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="66">
+        <f>B17/B16*B18</f>
+        <v>104.77611940298507</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="66">
+        <f>B18/B20</f>
+        <v>72</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="66">
+        <f>B16/B20</f>
+        <v>134</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="66">
+        <f>B23-B17</f>
+        <v>-61</v>
+      </c>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:K14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>